--- a/mode_docx_gen/pmi_dzt/part/tdif/hf5phar1/HF5PHAR1.xlsx
+++ b/mode_docx_gen/pmi_dzt/part/tdif/hf5phar1/HF5PHAR1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="108">
   <si>
     <t>Категория (group)</t>
   </si>
@@ -160,9 +160,6 @@
     <t>FLOAT32</t>
   </si>
   <si>
-    <t>%</t>
-  </si>
-  <si>
     <t>ASG</t>
   </si>
   <si>
@@ -238,9 +235,6 @@
     <t>Выдержка времени ввода перекрестной блокировки</t>
   </si>
   <si>
-    <t>с</t>
-  </si>
-  <si>
     <t>CrossBlkDlTmms</t>
   </si>
   <si>
@@ -332,6 +326,24 @@
   </si>
   <si>
     <t>Ratio</t>
+  </si>
+  <si>
+    <t>о.е.</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>мс</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>0.4</t>
+  </si>
+  <si>
+    <t>0.25</t>
   </si>
 </sst>
 </file>
@@ -354,7 +366,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -382,6 +394,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -437,7 +455,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -453,6 +471,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -861,7 +880,7 @@
         <v>29</v>
       </c>
       <c r="AE1" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -869,46 +888,46 @@
         <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="3">
-        <v>5</v>
-      </c>
-      <c r="J2" s="3">
-        <v>40</v>
-      </c>
-      <c r="K2" s="3">
-        <v>1</v>
-      </c>
-      <c r="L2" s="3">
-        <v>25</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>45</v>
@@ -917,7 +936,7 @@
         <v>32</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>39</v>
@@ -944,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AC2" s="3" t="s">
         <v>32</v>
@@ -956,7 +975,7 @@
         <v>32</v>
       </c>
       <c r="AE2" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -964,55 +983,55 @@
         <v>44</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>1</v>
+      </c>
+      <c r="K3" s="3">
+        <v>1</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3">
-        <v>1</v>
-      </c>
-      <c r="K3" s="3">
-        <v>1</v>
-      </c>
-      <c r="L3" s="3">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="N3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="O3" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="P3" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>32</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>39</v>
@@ -1039,10 +1058,10 @@
         <v>0</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AC3" s="3" t="s">
         <v>32</v>
@@ -1056,55 +1075,55 @@
         <v>44</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="I4" s="9">
+        <v>60</v>
+      </c>
+      <c r="J4" s="9">
+        <v>4000</v>
+      </c>
+      <c r="K4" s="9">
+        <v>10</v>
+      </c>
+      <c r="L4" s="9">
+        <v>60</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0.06</v>
-      </c>
-      <c r="J4" s="3">
-        <v>4</v>
-      </c>
-      <c r="K4" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="L4" s="3">
-        <v>0.06</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="O4" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Q4" s="3" t="s">
         <v>32</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>39</v>
@@ -1131,10 +1150,10 @@
         <v>0</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AC4" s="3" t="s">
         <v>32</v>
@@ -1143,7 +1162,7 @@
         <v>32</v>
       </c>
       <c r="AE4" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1151,41 +1170,41 @@
         <v>44</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9">
+        <v>100</v>
+      </c>
+      <c r="K5" s="9">
+        <v>1</v>
+      </c>
+      <c r="L5" s="9">
+        <v>15</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K5" s="3">
-        <v>1E-3</v>
-      </c>
-      <c r="L5" s="3">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="N5" s="3" t="s">
         <v>32</v>
       </c>
@@ -1226,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AB5" s="3" t="s">
         <v>32</v>
@@ -1238,7 +1257,7 @@
         <v>32</v>
       </c>
       <c r="AE5" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:31" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1246,10 +1265,10 @@
         <v>30</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>31</v>
@@ -1279,7 +1298,7 @@
         <v>32</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>34</v>
@@ -1321,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AB6" s="4" t="s">
         <v>40</v>
@@ -1338,10 +1357,10 @@
         <v>30</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>41</v>
@@ -1371,7 +1390,7 @@
         <v>32</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N7" s="4" t="s">
         <v>34</v>
@@ -1413,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="AA7" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AB7" s="4" t="s">
         <v>43</v>
@@ -1430,49 +1449,49 @@
         <v>30</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="N8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="N8" s="4" t="s">
+      <c r="O8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="P8" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="Q8" s="4" t="s">
         <v>32</v>
@@ -1505,10 +1524,10 @@
         <v>1</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AB8" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AC8" s="4" t="s">
         <v>32</v>
@@ -1522,49 +1541,49 @@
         <v>30</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="N9" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="O9" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q9" s="4" t="s">
         <v>32</v>
@@ -1597,10 +1616,10 @@
         <v>1</v>
       </c>
       <c r="AA9" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AB9" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AC9" s="4" t="s">
         <v>32</v>
@@ -1614,49 +1633,49 @@
         <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="N10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="O10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="P10" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q10" s="4" t="s">
         <v>32</v>
@@ -1689,10 +1708,10 @@
         <v>1</v>
       </c>
       <c r="AA10" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AB10" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AC10" s="4" t="s">
         <v>32</v>
@@ -1706,49 +1725,49 @@
         <v>30</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="N11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="O11" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="P11" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q11" s="4" t="s">
         <v>32</v>
@@ -1781,10 +1800,10 @@
         <v>1</v>
       </c>
       <c r="AA11" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AB11" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AC11" s="4" t="s">
         <v>32</v>
@@ -1812,44 +1831,44 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" t="s">
         <v>97</v>
-      </c>
-      <c r="B5" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B6">
         <v>40</v>

--- a/mode_docx_gen/pmi_dzt/part/tdif/hf5phar1/HF5PHAR1.xlsx
+++ b/mode_docx_gen/pmi_dzt/part/tdif/hf5phar1/HF5PHAR1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="104">
   <si>
     <t>Категория (group)</t>
   </si>
@@ -331,19 +331,7 @@
     <t>о.е.</t>
   </si>
   <si>
-    <t>0.01</t>
-  </si>
-  <si>
     <t>мс</t>
-  </si>
-  <si>
-    <t>0.05</t>
-  </si>
-  <si>
-    <t>0.4</t>
-  </si>
-  <si>
-    <t>0.25</t>
   </si>
 </sst>
 </file>
@@ -908,17 +896,17 @@
       <c r="H2" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>107</v>
+      <c r="I2" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="J2" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="K2" s="9">
+        <v>0.01</v>
+      </c>
+      <c r="L2" s="9">
+        <v>0.25</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>83</v>
@@ -1093,7 +1081,7 @@
         <v>68</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I4" s="9">
         <v>60</v>
@@ -1188,7 +1176,7 @@
         <v>68</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I5" s="9">
         <v>0</v>
